--- a/evidence/AZ-100-05-003.xlsx
+++ b/evidence/AZ-100-05-003.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-24T23:17:44.020Z</t>
+          <t>2026-10-25T02:20:13.200Z</t>
         </is>
       </c>
     </row>
